--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,6 +790,103 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126369086</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58159</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102995</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Buskskvätta</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Saxicola rubetra</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gyllingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>495655</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6719196</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,6 +888,200 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126387970</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98269</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gyllingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>495728</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6719297</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126388887</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58025</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gyllingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>495728</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6719297</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>126369086</v>
       </c>
       <c r="B3" t="n">
-        <v>58159</v>
+        <v>58162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>126387970</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>126388887</v>
       </c>
       <c r="B5" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1082,6 +1082,113 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128402178</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57803</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gyllingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>495728</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6719297</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -1087,7 +1087,7 @@
         <v>128402178</v>
       </c>
       <c r="B6" t="n">
-        <v>57803</v>
+        <v>57815</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -1087,7 +1087,7 @@
         <v>128402178</v>
       </c>
       <c r="B6" t="n">
-        <v>57815</v>
+        <v>57819</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -1087,7 +1087,7 @@
         <v>128402178</v>
       </c>
       <c r="B6" t="n">
-        <v>57819</v>
+        <v>57846</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -1087,7 +1087,7 @@
         <v>128402178</v>
       </c>
       <c r="B6" t="n">
-        <v>57846</v>
+        <v>57850</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -1087,7 +1087,7 @@
         <v>128402178</v>
       </c>
       <c r="B6" t="n">
-        <v>57850</v>
+        <v>57853</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -1091,7 +1091,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111126026</v>
+        <v>126457812</v>
       </c>
       <c r="B2" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>102980</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495674.2305998703</v>
+        <v>495654</v>
       </c>
       <c r="R2" t="n">
-        <v>6719224.523268029</v>
+        <v>6719285</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>18:05</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>18:05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2 blommande och drygt 40 bladrosetter</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -796,11 +775,11 @@
         <v>126369086</v>
       </c>
       <c r="B3" t="n">
-        <v>58162</v>
+        <v>58463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -890,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126387970</v>
+        <v>126388887</v>
       </c>
       <c r="B4" t="n">
-        <v>98278</v>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -901,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -955,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126388887</v>
+        <v>126388902</v>
       </c>
       <c r="B5" t="n">
-        <v>58027</v>
+        <v>58439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -998,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103018</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1022,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495728</v>
+        <v>495654</v>
       </c>
       <c r="R5" t="n">
-        <v>6719297</v>
+        <v>6719285</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128402178</v>
+        <v>126487035</v>
       </c>
       <c r="B6" t="n">
-        <v>57853</v>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1095,37 +1074,49 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205976</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495728</v>
+        <v>495654</v>
       </c>
       <c r="R6" t="n">
-        <v>6719297</v>
+        <v>6719285</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1149,22 +1140,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,6 +1179,1052 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126522050</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gyllingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>495654</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6719285</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128412408</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gyllingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>495650</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6719267</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133065918</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58671</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103057</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sävsparv</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Emberiza schoeniclus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gyllingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>495650</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6719267</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm, Stina Dalmalm</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128402178</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gyllingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>495728</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6719297</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127520634</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gyllingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>495650</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6719267</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>111173602</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56884</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gyllingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>495647</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6719274</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-07-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-07-29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>124240901</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56884</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gyllingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>495640</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6719238</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Skogsödlor har observerats på platsen under många år.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm, Johan Liljeroos</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126387970</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gyllingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>495728</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6719297</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>111126026</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gyllingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>495674</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6719224</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2 blommande och drygt 40 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126387781</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gyllingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>495654</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6719285</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1182,48 +1182,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126522050</v>
+        <v>134493111</v>
       </c>
       <c r="B7" t="n">
-        <v>58636</v>
+        <v>58136</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495654</v>
+        <v>495728</v>
       </c>
       <c r="R7" t="n">
-        <v>6719285</v>
+        <v>6719297</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1247,22 +1252,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1289,7 +1294,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128412408</v>
+        <v>126522050</v>
       </c>
       <c r="B8" t="n">
         <v>58636</v>
@@ -1324,13 +1329,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495650</v>
+        <v>495654</v>
       </c>
       <c r="R8" t="n">
-        <v>6719267</v>
+        <v>6719285</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1354,22 +1359,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1396,10 +1401,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133065918</v>
+        <v>128412408</v>
       </c>
       <c r="B9" t="n">
-        <v>58671</v>
+        <v>58636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1407,16 +1412,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103057</v>
+        <v>103044</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1425,11 +1430,6 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
@@ -1466,12 +1466,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,17 +1501,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm, Stina Dalmalm</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128402178</v>
+        <v>133065918</v>
       </c>
       <c r="B10" t="n">
-        <v>58085</v>
+        <v>58671</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1509,37 +1519,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205976</v>
+        <v>103057</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495728</v>
+        <v>495650</v>
       </c>
       <c r="R10" t="n">
-        <v>6719297</v>
+        <v>6719267</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1563,22 +1578,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>08:36</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>08:36</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1598,39 +1603,39 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm</t>
+          <t>Johanna Dalmalm, Stina Dalmalm</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127520634</v>
+        <v>128402178</v>
       </c>
       <c r="B11" t="n">
-        <v>56837</v>
+        <v>58085</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>206002</v>
+        <v>205976</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1640,13 +1645,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495650</v>
+        <v>495728</v>
       </c>
       <c r="R11" t="n">
-        <v>6719267</v>
+        <v>6719297</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1670,12 +1675,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1702,58 +1717,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111173602</v>
+        <v>127520634</v>
       </c>
       <c r="B12" t="n">
-        <v>56884</v>
+        <v>56837</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>208255</v>
+        <v>206002</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495647</v>
+        <v>495650</v>
       </c>
       <c r="R12" t="n">
-        <v>6719274</v>
+        <v>6719267</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1777,12 +1782,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1797,19 +1802,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124240901</v>
+        <v>111173602</v>
       </c>
       <c r="B13" t="n">
         <v>56884</v>
@@ -1842,24 +1847,25 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495640</v>
+        <v>495647</v>
       </c>
       <c r="R13" t="n">
-        <v>6719238</v>
+        <v>6719274</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1883,17 +1889,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Skogsödlor har observerats på platsen under många år.</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1902,29 +1903,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm, Johan Liljeroos</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126387970</v>
+        <v>124240901</v>
       </c>
       <c r="B14" t="n">
-        <v>99035</v>
+        <v>56884</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1932,37 +1932,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>208255</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495728</v>
+        <v>495640</v>
       </c>
       <c r="R14" t="n">
-        <v>6719297</v>
+        <v>6719238</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1986,12 +1995,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Skogsödlor har observerats på platsen under många år.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2000,6 +2014,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2011,56 +2026,60 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm</t>
+          <t>Johanna Dalmalm, Johan Liljeroos</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111126026</v>
+        <v>134499476</v>
       </c>
       <c r="B15" t="n">
-        <v>99118</v>
+        <v>56925</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>208260</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495674</v>
+        <v>495650</v>
       </c>
       <c r="R15" t="n">
-        <v>6719224</v>
+        <v>6719267</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2084,27 +2103,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:05</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>2 blommande och drygt 40 bladrosetter</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2119,22 +2133,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126387781</v>
+        <v>126387970</v>
       </c>
       <c r="B16" t="n">
-        <v>97983</v>
+        <v>99035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2142,21 +2156,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2166,13 +2180,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495654</v>
+        <v>495728</v>
       </c>
       <c r="R16" t="n">
-        <v>6719285</v>
+        <v>6719297</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2225,6 +2239,216 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>111126026</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gyllingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>495674</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6719224</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2 blommande och drygt 40 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126387781</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gyllingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>495654</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6719285</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,48 +869,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126388887</v>
+        <v>134516427</v>
       </c>
       <c r="B4" t="n">
-        <v>58327</v>
+        <v>58410</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495728</v>
+        <v>495640</v>
       </c>
       <c r="R4" t="n">
-        <v>6719297</v>
+        <v>6719238</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -934,12 +939,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126388902</v>
+        <v>126388887</v>
       </c>
       <c r="B5" t="n">
-        <v>58439</v>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1016,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495654</v>
+        <v>495728</v>
       </c>
       <c r="R5" t="n">
-        <v>6719285</v>
+        <v>6719297</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1063,47 +1078,35 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126487035</v>
+        <v>126388902</v>
       </c>
       <c r="B6" t="n">
-        <v>58114</v>
+        <v>58439</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103018</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
@@ -1140,22 +1143,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:47</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:47</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1182,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134493111</v>
+        <v>126487035</v>
       </c>
       <c r="B7" t="n">
-        <v>58136</v>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1210,25 +1203,32 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495728</v>
+        <v>495654</v>
       </c>
       <c r="R7" t="n">
-        <v>6719297</v>
+        <v>6719285</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1252,22 +1252,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1294,48 +1294,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126522050</v>
+        <v>134493111</v>
       </c>
       <c r="B8" t="n">
-        <v>58636</v>
+        <v>58136</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495654</v>
+        <v>495728</v>
       </c>
       <c r="R8" t="n">
-        <v>6719285</v>
+        <v>6719297</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1359,22 +1364,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1401,7 +1406,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128412408</v>
+        <v>126522050</v>
       </c>
       <c r="B9" t="n">
         <v>58636</v>
@@ -1436,13 +1441,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495650</v>
+        <v>495654</v>
       </c>
       <c r="R9" t="n">
-        <v>6719267</v>
+        <v>6719285</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1466,22 +1471,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1508,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133065918</v>
+        <v>128412408</v>
       </c>
       <c r="B10" t="n">
-        <v>58671</v>
+        <v>58636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1519,16 +1524,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103057</v>
+        <v>103044</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1537,11 +1542,6 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
@@ -1578,12 +1578,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,17 +1613,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm, Stina Dalmalm</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128402178</v>
+        <v>133065918</v>
       </c>
       <c r="B11" t="n">
-        <v>58085</v>
+        <v>58671</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1621,37 +1631,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205976</v>
+        <v>103057</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495728</v>
+        <v>495650</v>
       </c>
       <c r="R11" t="n">
-        <v>6719297</v>
+        <v>6719267</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1675,22 +1690,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>08:36</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>08:36</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1710,39 +1715,39 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm</t>
+          <t>Johanna Dalmalm, Stina Dalmalm</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127520634</v>
+        <v>128402178</v>
       </c>
       <c r="B12" t="n">
-        <v>56837</v>
+        <v>58085</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>206002</v>
+        <v>205976</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1752,13 +1757,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495650</v>
+        <v>495728</v>
       </c>
       <c r="R12" t="n">
-        <v>6719267</v>
+        <v>6719297</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1782,12 +1787,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1814,58 +1829,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111173602</v>
+        <v>127520634</v>
       </c>
       <c r="B13" t="n">
-        <v>56884</v>
+        <v>56837</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>208255</v>
+        <v>206002</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495647</v>
+        <v>495650</v>
       </c>
       <c r="R13" t="n">
-        <v>6719274</v>
+        <v>6719267</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1889,12 +1894,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1909,19 +1914,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124240901</v>
+        <v>111173602</v>
       </c>
       <c r="B14" t="n">
         <v>56884</v>
@@ -1954,24 +1959,25 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495640</v>
+        <v>495647</v>
       </c>
       <c r="R14" t="n">
-        <v>6719238</v>
+        <v>6719274</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1995,17 +2001,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Skogsödlor har observerats på platsen under många år.</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2014,29 +2015,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm, Johan Liljeroos</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134499476</v>
+        <v>124240901</v>
       </c>
       <c r="B15" t="n">
-        <v>56925</v>
+        <v>56884</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2044,39 +2044,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>208260</v>
+        <v>208255</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495650</v>
+        <v>495640</v>
       </c>
       <c r="R15" t="n">
-        <v>6719267</v>
+        <v>6719238</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2103,22 +2107,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:51</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:51</t>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Skogsödlor har observerats på platsen under många år.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2127,6 +2126,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2138,17 +2138,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm</t>
+          <t>Johanna Dalmalm, Johan Liljeroos</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126387970</v>
+        <v>134499476</v>
       </c>
       <c r="B16" t="n">
-        <v>99035</v>
+        <v>56925</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2156,37 +2156,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>208260</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495728</v>
+        <v>495650</v>
       </c>
       <c r="R16" t="n">
-        <v>6719297</v>
+        <v>6719267</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2210,12 +2215,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2242,49 +2257,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111126026</v>
+        <v>126387970</v>
       </c>
       <c r="B17" t="n">
-        <v>99118</v>
+        <v>99035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495674</v>
+        <v>495728</v>
       </c>
       <c r="R17" t="n">
-        <v>6719224</v>
+        <v>6719297</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2308,27 +2322,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>18:05</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>18:05</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>2 blommande och drygt 40 bladrosetter</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2343,60 +2342,61 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126387781</v>
+        <v>111126026</v>
       </c>
       <c r="B18" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495654</v>
+        <v>495674</v>
       </c>
       <c r="R18" t="n">
-        <v>6719285</v>
+        <v>6719224</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2420,12 +2420,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2 blommande och drygt 40 bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2440,15 +2455,112 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126387781</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gyllingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>495654</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6719285</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -981,48 +981,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126388887</v>
+        <v>134811381</v>
       </c>
       <c r="B5" t="n">
-        <v>58327</v>
+        <v>58410</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495728</v>
+        <v>495654</v>
       </c>
       <c r="R5" t="n">
-        <v>6719297</v>
+        <v>6719285</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1046,12 +1051,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126388902</v>
+        <v>126388887</v>
       </c>
       <c r="B6" t="n">
-        <v>58439</v>
+        <v>58327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495654</v>
+        <v>495728</v>
       </c>
       <c r="R6" t="n">
-        <v>6719285</v>
+        <v>6719297</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1175,47 +1190,35 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126487035</v>
+        <v>126388902</v>
       </c>
       <c r="B7" t="n">
-        <v>58114</v>
+        <v>58439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>103018</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
@@ -1252,22 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:47</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:47</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1294,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134493111</v>
+        <v>126487035</v>
       </c>
       <c r="B8" t="n">
-        <v>58136</v>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,25 +1315,32 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495728</v>
+        <v>495654</v>
       </c>
       <c r="R8" t="n">
-        <v>6719297</v>
+        <v>6719285</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1364,22 +1364,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1406,48 +1406,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126522050</v>
+        <v>134493111</v>
       </c>
       <c r="B9" t="n">
-        <v>58636</v>
+        <v>58136</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495654</v>
+        <v>495728</v>
       </c>
       <c r="R9" t="n">
-        <v>6719285</v>
+        <v>6719297</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1471,22 +1476,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1513,7 +1518,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128412408</v>
+        <v>126522050</v>
       </c>
       <c r="B10" t="n">
         <v>58636</v>
@@ -1548,13 +1553,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495650</v>
+        <v>495654</v>
       </c>
       <c r="R10" t="n">
-        <v>6719267</v>
+        <v>6719285</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1578,22 +1583,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1620,10 +1625,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133065918</v>
+        <v>128412408</v>
       </c>
       <c r="B11" t="n">
-        <v>58671</v>
+        <v>58636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1631,16 +1636,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103057</v>
+        <v>103044</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1649,11 +1654,6 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
@@ -1690,12 +1690,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1715,17 +1725,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm, Stina Dalmalm</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128402178</v>
+        <v>133065918</v>
       </c>
       <c r="B12" t="n">
-        <v>58085</v>
+        <v>58671</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1733,37 +1743,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>205976</v>
+        <v>103057</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495728</v>
+        <v>495650</v>
       </c>
       <c r="R12" t="n">
-        <v>6719297</v>
+        <v>6719267</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1787,22 +1802,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>08:36</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>08:36</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,39 +1827,39 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm</t>
+          <t>Johanna Dalmalm, Stina Dalmalm</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127520634</v>
+        <v>128402178</v>
       </c>
       <c r="B13" t="n">
-        <v>56837</v>
+        <v>58085</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>206002</v>
+        <v>205976</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1864,13 +1869,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495650</v>
+        <v>495728</v>
       </c>
       <c r="R13" t="n">
-        <v>6719267</v>
+        <v>6719297</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1894,12 +1899,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1926,58 +1941,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111173602</v>
+        <v>127520634</v>
       </c>
       <c r="B14" t="n">
-        <v>56884</v>
+        <v>56837</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>208255</v>
+        <v>206002</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495647</v>
+        <v>495650</v>
       </c>
       <c r="R14" t="n">
-        <v>6719274</v>
+        <v>6719267</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2001,12 +2006,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2021,19 +2026,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124240901</v>
+        <v>111173602</v>
       </c>
       <c r="B15" t="n">
         <v>56884</v>
@@ -2066,24 +2071,25 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495640</v>
+        <v>495647</v>
       </c>
       <c r="R15" t="n">
-        <v>6719238</v>
+        <v>6719274</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2107,17 +2113,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Skogsödlor har observerats på platsen under många år.</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2126,29 +2127,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm, Johan Liljeroos</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134499476</v>
+        <v>124240901</v>
       </c>
       <c r="B16" t="n">
-        <v>56925</v>
+        <v>56884</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2156,39 +2156,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208260</v>
+        <v>208255</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495650</v>
+        <v>495640</v>
       </c>
       <c r="R16" t="n">
-        <v>6719267</v>
+        <v>6719238</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2215,22 +2219,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:51</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:51</t>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Skogsödlor har observerats på platsen under många år.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2239,6 +2238,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2250,17 +2250,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm</t>
+          <t>Johanna Dalmalm, Johan Liljeroos</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126387970</v>
+        <v>134499476</v>
       </c>
       <c r="B17" t="n">
-        <v>99035</v>
+        <v>56925</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2268,37 +2268,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>208260</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495728</v>
+        <v>495650</v>
       </c>
       <c r="R17" t="n">
-        <v>6719297</v>
+        <v>6719267</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2322,12 +2327,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2354,49 +2369,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111126026</v>
+        <v>126387970</v>
       </c>
       <c r="B18" t="n">
-        <v>99118</v>
+        <v>99035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495674</v>
+        <v>495728</v>
       </c>
       <c r="R18" t="n">
-        <v>6719224</v>
+        <v>6719297</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2420,27 +2434,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>18:05</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>18:05</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>2 blommande och drygt 40 bladrosetter</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2455,60 +2454,61 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126387781</v>
+        <v>111126026</v>
       </c>
       <c r="B19" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495654</v>
+        <v>495674</v>
       </c>
       <c r="R19" t="n">
-        <v>6719285</v>
+        <v>6719224</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2532,12 +2532,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2 blommande och drygt 40 bladrosetter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2552,15 +2567,112 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126387781</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gyllingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>495654</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6719285</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1518,10 +1518,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126522050</v>
+        <v>135251208</v>
       </c>
       <c r="B10" t="n">
-        <v>58636</v>
+        <v>58131</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1529,16 +1529,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103044</v>
+        <v>103023</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1547,19 +1547,24 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495654</v>
+        <v>495650</v>
       </c>
       <c r="R10" t="n">
-        <v>6719285</v>
+        <v>6719267</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1583,22 +1588,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1625,7 +1630,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128412408</v>
+        <v>126522050</v>
       </c>
       <c r="B11" t="n">
         <v>58636</v>
@@ -1660,13 +1665,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495650</v>
+        <v>495654</v>
       </c>
       <c r="R11" t="n">
-        <v>6719267</v>
+        <v>6719285</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1690,22 +1695,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1732,10 +1737,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133065918</v>
+        <v>128412408</v>
       </c>
       <c r="B12" t="n">
-        <v>58671</v>
+        <v>58636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1743,16 +1748,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103057</v>
+        <v>103044</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1761,11 +1766,6 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
@@ -1802,12 +1802,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,17 +1837,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm, Stina Dalmalm</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128402178</v>
+        <v>133065918</v>
       </c>
       <c r="B13" t="n">
-        <v>58085</v>
+        <v>58671</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1845,37 +1855,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205976</v>
+        <v>103057</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495728</v>
+        <v>495650</v>
       </c>
       <c r="R13" t="n">
-        <v>6719297</v>
+        <v>6719267</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1899,22 +1914,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>08:36</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>08:36</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,39 +1939,39 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm</t>
+          <t>Johanna Dalmalm, Stina Dalmalm</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127520634</v>
+        <v>128402178</v>
       </c>
       <c r="B14" t="n">
-        <v>56837</v>
+        <v>58085</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>206002</v>
+        <v>205976</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1976,13 +1981,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495650</v>
+        <v>495728</v>
       </c>
       <c r="R14" t="n">
-        <v>6719267</v>
+        <v>6719297</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2006,12 +2011,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2038,58 +2053,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111173602</v>
+        <v>127520634</v>
       </c>
       <c r="B15" t="n">
-        <v>56884</v>
+        <v>56837</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>208255</v>
+        <v>206002</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495647</v>
+        <v>495650</v>
       </c>
       <c r="R15" t="n">
-        <v>6719274</v>
+        <v>6719267</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2113,12 +2118,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2133,19 +2138,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124240901</v>
+        <v>111173602</v>
       </c>
       <c r="B16" t="n">
         <v>56884</v>
@@ -2178,24 +2183,25 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495640</v>
+        <v>495647</v>
       </c>
       <c r="R16" t="n">
-        <v>6719238</v>
+        <v>6719274</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2219,17 +2225,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Skogsödlor har observerats på platsen under många år.</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2238,29 +2239,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm, Johan Liljeroos</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134499476</v>
+        <v>124240901</v>
       </c>
       <c r="B17" t="n">
-        <v>56925</v>
+        <v>56884</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2268,39 +2268,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>208260</v>
+        <v>208255</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495650</v>
+        <v>495640</v>
       </c>
       <c r="R17" t="n">
-        <v>6719267</v>
+        <v>6719238</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2327,22 +2331,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:51</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:51</t>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Skogsödlor har observerats på platsen under många år.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2351,6 +2350,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2362,17 +2362,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm</t>
+          <t>Johanna Dalmalm, Johan Liljeroos</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126387970</v>
+        <v>134499476</v>
       </c>
       <c r="B18" t="n">
-        <v>99035</v>
+        <v>56925</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2380,37 +2380,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>208260</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495728</v>
+        <v>495650</v>
       </c>
       <c r="R18" t="n">
-        <v>6719297</v>
+        <v>6719267</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2434,12 +2439,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2466,10 +2481,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134837603</v>
+        <v>126387970</v>
       </c>
       <c r="B19" t="n">
-        <v>99112</v>
+        <v>99035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2495,24 +2510,19 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495654</v>
+        <v>495728</v>
       </c>
       <c r="R19" t="n">
-        <v>6719285</v>
+        <v>6719297</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2536,22 +2546,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>18:36</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>18:36</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2578,10 +2578,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134881502</v>
+        <v>134837603</v>
       </c>
       <c r="B20" t="n">
-        <v>99219</v>
+        <v>99112</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2648,22 +2648,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2690,49 +2690,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111126026</v>
+        <v>134881502</v>
       </c>
       <c r="B21" t="n">
-        <v>99118</v>
+        <v>99219</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495674</v>
+        <v>495654</v>
       </c>
       <c r="R21" t="n">
-        <v>6719224</v>
+        <v>6719285</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2756,27 +2760,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:05</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2 blommande och drygt 40 bladrosetter</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2791,60 +2790,61 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126387781</v>
+        <v>111126026</v>
       </c>
       <c r="B22" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495654</v>
+        <v>495674</v>
       </c>
       <c r="R22" t="n">
-        <v>6719285</v>
+        <v>6719224</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2868,12 +2868,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2 blommande och drygt 40 bladrosetter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2888,15 +2903,224 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135252650</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gyllingen, Gyllingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>495788</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6719206</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126387781</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gyllingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>495654</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6719285</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3027,48 +3027,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126387781</v>
+        <v>135323748</v>
       </c>
       <c r="B24" t="n">
-        <v>97983</v>
+        <v>99195</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gyllingen, Dlr</t>
+          <t>Knärot Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495654</v>
+        <v>495693</v>
       </c>
       <c r="R24" t="n">
-        <v>6719285</v>
+        <v>6719205</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3092,12 +3097,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,6 +3136,103 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126387781</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Gyllingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>495654</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6719285</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126457812</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126369086</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134516427</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134811381</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126388887</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126388902</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1403,6 +1438,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126487035</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1515,6 +1555,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493111</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1627,6 +1672,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251208</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1734,6 +1784,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126522050</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1841,6 +1896,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128412408</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1943,6 +2003,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133065918</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2050,6 +2115,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128402178</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2147,6 +2217,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127520634</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2254,6 +2329,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111173602</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2366,6 +2446,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124240901</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2478,6 +2563,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134499476</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2575,6 +2665,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126387970</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2687,6 +2782,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134837603</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2799,6 +2899,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134881502</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2912,6 +3017,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111126026</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3024,6 +3134,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252650</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3136,6 +3251,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323748</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3233,8 +3353,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126387781</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -1566,7 +1566,7 @@
         <v>135251208</v>
       </c>
       <c r="B10" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>135252650</v>
       </c>
       <c r="B23" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>135323748</v>
       </c>
       <c r="B24" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -3028,7 +3028,7 @@
         <v>135252650</v>
       </c>
       <c r="B23" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>135323748</v>
       </c>
       <c r="B24" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ22"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126522050</v>
+        <v>135251208</v>
       </c>
       <c r="B10" t="n">
-        <v>58636</v>
+        <v>58136</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,16 +1574,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103044</v>
+        <v>103023</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1592,19 +1592,24 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495654</v>
+        <v>495650</v>
       </c>
       <c r="R10" t="n">
-        <v>6719285</v>
+        <v>6719267</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1628,22 +1633,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1669,13 +1674,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126522050</t>
+          <t>https://artportalen.se/Sighting/135251208</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128412408</v>
+        <v>126522050</v>
       </c>
       <c r="B11" t="n">
         <v>58636</v>
@@ -1710,13 +1715,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495650</v>
+        <v>495654</v>
       </c>
       <c r="R11" t="n">
-        <v>6719267</v>
+        <v>6719285</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1740,22 +1745,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,16 +1786,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128412408</t>
+          <t>https://artportalen.se/Sighting/126522050</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133065918</v>
+        <v>128412408</v>
       </c>
       <c r="B12" t="n">
-        <v>58671</v>
+        <v>58636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1798,16 +1803,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103057</v>
+        <v>103044</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1816,11 +1821,6 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
@@ -1857,12 +1857,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,22 +1892,22 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm, Stina Dalmalm</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133065918</t>
+          <t>https://artportalen.se/Sighting/128412408</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128402178</v>
+        <v>133065918</v>
       </c>
       <c r="B13" t="n">
-        <v>58085</v>
+        <v>58671</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1905,37 +1915,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205976</v>
+        <v>103057</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495728</v>
+        <v>495650</v>
       </c>
       <c r="R13" t="n">
-        <v>6719297</v>
+        <v>6719267</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1959,22 +1974,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>08:36</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>08:36</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1994,44 +1999,44 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm</t>
+          <t>Johanna Dalmalm, Stina Dalmalm</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128402178</t>
+          <t>https://artportalen.se/Sighting/133065918</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127520634</v>
+        <v>128402178</v>
       </c>
       <c r="B14" t="n">
-        <v>56837</v>
+        <v>58085</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>206002</v>
+        <v>205976</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2041,13 +2046,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495650</v>
+        <v>495728</v>
       </c>
       <c r="R14" t="n">
-        <v>6719267</v>
+        <v>6719297</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2071,12 +2076,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2102,64 +2117,54 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127520634</t>
+          <t>https://artportalen.se/Sighting/128402178</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111173602</v>
+        <v>127520634</v>
       </c>
       <c r="B15" t="n">
-        <v>56884</v>
+        <v>56837</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>208255</v>
+        <v>206002</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495647</v>
+        <v>495650</v>
       </c>
       <c r="R15" t="n">
-        <v>6719274</v>
+        <v>6719267</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2183,12 +2188,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,24 +2208,24 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111173602</t>
+          <t>https://artportalen.se/Sighting/127520634</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124240901</v>
+        <v>111173602</v>
       </c>
       <c r="B16" t="n">
         <v>56884</v>
@@ -2253,24 +2258,25 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495640</v>
+        <v>495647</v>
       </c>
       <c r="R16" t="n">
-        <v>6719238</v>
+        <v>6719274</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2294,17 +2300,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Skogsödlor har observerats på platsen under många år.</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2313,34 +2314,33 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm, Johan Liljeroos</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124240901</t>
+          <t>https://artportalen.se/Sighting/111173602</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134499476</v>
+        <v>124240901</v>
       </c>
       <c r="B17" t="n">
-        <v>56925</v>
+        <v>56884</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2348,39 +2348,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>208260</v>
+        <v>208255</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495650</v>
+        <v>495640</v>
       </c>
       <c r="R17" t="n">
-        <v>6719267</v>
+        <v>6719238</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2407,22 +2411,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:51</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:51</t>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Skogsödlor har observerats på platsen under många år.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2431,6 +2430,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2442,22 +2442,22 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm</t>
+          <t>Johanna Dalmalm, Johan Liljeroos</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134499476</t>
+          <t>https://artportalen.se/Sighting/124240901</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126387970</v>
+        <v>134499476</v>
       </c>
       <c r="B18" t="n">
-        <v>99035</v>
+        <v>56925</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2465,37 +2465,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>208260</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495728</v>
+        <v>495650</v>
       </c>
       <c r="R18" t="n">
-        <v>6719297</v>
+        <v>6719267</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2519,12 +2524,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2550,16 +2565,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126387970</t>
+          <t>https://artportalen.se/Sighting/134499476</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134837603</v>
+        <v>126387970</v>
       </c>
       <c r="B19" t="n">
-        <v>99112</v>
+        <v>99035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,24 +2600,19 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495654</v>
+        <v>495728</v>
       </c>
       <c r="R19" t="n">
-        <v>6719285</v>
+        <v>6719297</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2626,22 +2636,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>18:36</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>18:36</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2667,16 +2667,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134837603</t>
+          <t>https://artportalen.se/Sighting/126387970</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134881502</v>
+        <v>134837603</v>
       </c>
       <c r="B20" t="n">
-        <v>99219</v>
+        <v>99112</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2684,21 +2684,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2743,22 +2743,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2784,55 +2784,59 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134881502</t>
+          <t>https://artportalen.se/Sighting/134837603</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111126026</v>
+        <v>134881502</v>
       </c>
       <c r="B21" t="n">
-        <v>99118</v>
+        <v>99219</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495674</v>
+        <v>495654</v>
       </c>
       <c r="R21" t="n">
-        <v>6719224</v>
+        <v>6719285</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2856,27 +2860,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:05</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2 blommande och drygt 40 bladrosetter</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2891,65 +2890,66 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111126026</t>
+          <t>https://artportalen.se/Sighting/134881502</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126387781</v>
+        <v>111126026</v>
       </c>
       <c r="B22" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gyllingen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495654</v>
+        <v>495674</v>
       </c>
       <c r="R22" t="n">
-        <v>6719285</v>
+        <v>6719224</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2973,12 +2973,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2 blommande och drygt 40 bladrosetter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2993,16 +3008,352 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johanna Dalmalm</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111126026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135252650</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gyllingen, Gyllingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>495788</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6719206</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135252650</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135323748</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Knärot Gyllingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>495693</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6719205</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323748</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126387781</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Gyllingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>495654</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6719285</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Johanna Dalmalm</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126387781</t>
         </is>
@@ -3031,6 +3382,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8529-2023 artfynd.xlsx
+++ b/artfynd/A 8529-2023 artfynd.xlsx
@@ -3028,7 +3028,7 @@
         <v>135252650</v>
       </c>
       <c r="B23" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>135323748</v>
       </c>
       <c r="B24" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
